--- a/Assets/Excel/monster_explore.xlsx
+++ b/Assets/Excel/monster_explore.xlsx
@@ -10,7 +10,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
   <si>
     <t>工作ID</t>
   </si>
@@ -96,6 +96,9 @@
     <t>地区名称</t>
   </si>
   <si>
+    <t>子地点名</t>
+  </si>
+  <si>
     <t>卡片标题</t>
   </si>
   <si>
@@ -129,6 +132,9 @@
     <t>sceneName</t>
   </si>
   <si>
+    <t>spotName</t>
+  </si>
+  <si>
     <t>displayName</t>
   </si>
   <si>
@@ -160,6 +166,9 @@
   </si>
   <si>
     <t>林缘哨道</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>林缘哨道 · 布陷</t>
@@ -445,194 +454,212 @@
       <c r="L1" t="s">
         <v>35</v>
       </c>
+      <c r="M1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L2" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="M2" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3">
+        <v>52</v>
+      </c>
+      <c r="F3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3">
         <v>5</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>8</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>1</v>
       </c>
-      <c r="I3" t="s">
-        <v>51</v>
-      </c>
       <c r="J3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K3" t="s">
-        <v>53</v>
-      </c>
-      <c r="L3">
+        <v>55</v>
+      </c>
+      <c r="L3" t="s">
+        <v>56</v>
+      </c>
+      <c r="M3">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4">
+        <v>6</v>
+      </c>
+      <c r="H4">
+        <v>11</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K4" t="s">
+        <v>62</v>
+      </c>
+      <c r="L4" t="s">
         <v>56</v>
       </c>
-      <c r="E4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F4">
-        <v>6</v>
-      </c>
-      <c r="G4">
-        <v>11</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4" t="s">
-        <v>58</v>
-      </c>
-      <c r="J4" t="s">
-        <v>59</v>
-      </c>
-      <c r="K4" t="s">
-        <v>53</v>
-      </c>
-      <c r="L4">
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F5">
+        <v>52</v>
+      </c>
+      <c r="F5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G5">
         <v>7.5</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>16</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>6</v>
       </c>
-      <c r="I5" t="s">
-        <v>64</v>
-      </c>
       <c r="J5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K5" t="s">
-        <v>66</v>
-      </c>
-      <c r="L5">
+        <v>68</v>
+      </c>
+      <c r="L5" t="s">
+        <v>69</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G6">
+        <v>10</v>
+      </c>
+      <c r="H6">
+        <v>24</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6" t="s">
+        <v>74</v>
+      </c>
+      <c r="K6" t="s">
+        <v>75</v>
+      </c>
+      <c r="L6" t="s">
         <v>69</v>
       </c>
-      <c r="E6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>24</v>
-      </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="I6" t="s">
-        <v>71</v>
-      </c>
-      <c r="J6" t="s">
-        <v>72</v>
-      </c>
-      <c r="K6" t="s">
-        <v>66</v>
-      </c>
-      <c r="L6">
+      <c r="M6">
         <v>2</v>
       </c>
     </row>
@@ -648,50 +675,50 @@
         <v>24</v>
       </c>
       <c r="B1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D3">
         <v>0.82</v>
@@ -705,13 +732,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D4">
         <v>0.18</v>
@@ -725,13 +752,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D5">
         <v>0.06</v>
@@ -745,13 +772,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D6">
         <v>0.65</v>
@@ -765,13 +792,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D7">
         <v>0.35</v>
@@ -785,13 +812,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D8">
         <v>0.14</v>
@@ -805,13 +832,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D9">
         <v>0.05</v>
@@ -825,13 +852,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D10">
         <v>0.55</v>
@@ -845,13 +872,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D11">
         <v>0.48</v>
@@ -865,13 +892,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D12">
         <v>0.22</v>
@@ -885,13 +912,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D13">
         <v>0.04</v>
@@ -905,13 +932,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D14">
         <v>0.42</v>
@@ -925,13 +952,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D15">
         <v>0.38</v>
@@ -945,13 +972,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D16">
         <v>0.12</v>
@@ -965,13 +992,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B17" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D17">
         <v>0.03</v>

--- a/Assets/Excel/monster_explore.xlsx
+++ b/Assets/Excel/monster_explore.xlsx
@@ -10,7 +10,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
   <si>
     <t>工作ID</t>
   </si>
@@ -111,7 +111,7 @@
     <t>解锁所需工作等级</t>
   </si>
   <si>
-    <t>描述</t>
+    <t>详情文案(右侧)</t>
   </si>
   <si>
     <t>缩略图颜色</t>
@@ -123,6 +123,15 @@
     <t>消耗数量</t>
   </si>
   <si>
+    <t>金币概率0~1</t>
+  </si>
+  <si>
+    <t>金币最少</t>
+  </si>
+  <si>
+    <t>金币最多</t>
+  </si>
+  <si>
     <t>workId</t>
   </si>
   <si>
@@ -157,6 +166,15 @@
   </si>
   <si>
     <t>costAmount</t>
+  </si>
+  <si>
+    <t>goldChance</t>
+  </si>
+  <si>
+    <t>goldMin</t>
+  </si>
+  <si>
+    <t>goldMax</t>
   </si>
   <si>
     <t>explore_forest_edge</t>
@@ -457,66 +475,84 @@
       <c r="M1" t="s">
         <v>36</v>
       </c>
+      <c r="N1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P1" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="I2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M2" t="s">
-        <v>48</v>
+        <v>51</v>
+      </c>
+      <c r="N2" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -528,36 +564,45 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="K3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="L3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="M3">
         <v>1</v>
       </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" t="s">
         <v>58</v>
       </c>
-      <c r="D4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" t="s">
-        <v>52</v>
-      </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G4">
         <v>6</v>
@@ -569,36 +614,45 @@
         <v>3</v>
       </c>
       <c r="J4" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="K4" t="s">
+        <v>68</v>
+      </c>
+      <c r="L4" t="s">
         <v>62</v>
-      </c>
-      <c r="L4" t="s">
-        <v>56</v>
       </c>
       <c r="M4">
         <v>1</v>
       </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E5" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G5">
         <v>7.5</v>
@@ -610,36 +664,45 @@
         <v>6</v>
       </c>
       <c r="J5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K5" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="L5" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="M5">
         <v>1</v>
       </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E6" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F6" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G6">
         <v>10</v>
@@ -651,16 +714,25 @@
         <v>10</v>
       </c>
       <c r="J6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="K6" t="s">
+        <v>81</v>
+      </c>
+      <c r="L6" t="s">
         <v>75</v>
-      </c>
-      <c r="L6" t="s">
-        <v>69</v>
       </c>
       <c r="M6">
         <v>2</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -675,50 +747,50 @@
         <v>24</v>
       </c>
       <c r="B1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C1" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D3">
         <v>0.82</v>
@@ -732,13 +804,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D4">
         <v>0.18</v>
@@ -752,13 +824,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D5">
         <v>0.06</v>
@@ -772,13 +844,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D6">
         <v>0.65</v>
@@ -792,13 +864,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D7">
         <v>0.35</v>
@@ -812,13 +884,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D8">
         <v>0.14</v>
@@ -832,13 +904,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D9">
         <v>0.05</v>
@@ -852,13 +924,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D10">
         <v>0.55</v>
@@ -872,13 +944,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D11">
         <v>0.48</v>
@@ -892,13 +964,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D12">
         <v>0.22</v>
@@ -912,13 +984,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B13" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D13">
         <v>0.04</v>
@@ -932,13 +1004,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D14">
         <v>0.42</v>
@@ -952,13 +1024,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D15">
         <v>0.38</v>
@@ -972,13 +1044,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D16">
         <v>0.12</v>
@@ -992,13 +1064,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B17" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C17" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D17">
         <v>0.03</v>

--- a/Assets/Excel/monster_explore.xlsx
+++ b/Assets/Excel/monster_explore.xlsx
@@ -10,7 +10,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
   <si>
     <t>工作ID</t>
   </si>
@@ -114,7 +114,7 @@
     <t>详情文案(右侧)</t>
   </si>
   <si>
-    <t>缩略图颜色</t>
+    <t>缩略图(空=动作ID)</t>
   </si>
   <si>
     <t>消耗道具ID</t>
@@ -159,7 +159,7 @@
     <t>description</t>
   </si>
   <si>
-    <t>thumbColor</t>
+    <t>thumbImage</t>
   </si>
   <si>
     <t>costItemId</t>
@@ -195,9 +195,6 @@
     <t>村外林缘常有史莱姆出没。布下小陷阱，等魔物踩中后搜刮残骸。</t>
   </si>
   <si>
-    <t>#4A3428</t>
-  </si>
-  <si>
     <t>small_trap</t>
   </si>
   <si>
@@ -216,9 +213,6 @@
     <t>岔路口泥泞，魔物足迹杂乱。仍用小陷阱，但掉落种类更杂。</t>
   </si>
   <si>
-    <t>#3A4838</t>
-  </si>
-  <si>
     <t>explore_mine_mouth</t>
   </si>
   <si>
@@ -234,9 +228,6 @@
     <t>废弃矿道口盘踞着更凶的魔物，需大陷阱才能稳妥收网。</t>
   </si>
   <si>
-    <t>#504038</t>
-  </si>
-  <si>
     <t>large_trap</t>
   </si>
   <si>
@@ -253,9 +244,6 @@
   </si>
   <si>
     <t>裂隙边缘魔力紊乱，魔物更强也更稀有。大陷阱每次要消耗两份才够稳。</t>
-  </si>
-  <si>
-    <t>#583848</t>
   </si>
   <si>
     <t>道具ID</t>
@@ -567,10 +555,10 @@
         <v>60</v>
       </c>
       <c r="K3" t="s">
+        <v>58</v>
+      </c>
+      <c r="L3" t="s">
         <v>61</v>
-      </c>
-      <c r="L3" t="s">
-        <v>62</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -587,22 +575,22 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" t="s">
         <v>64</v>
-      </c>
-      <c r="D4" t="s">
-        <v>65</v>
       </c>
       <c r="E4" t="s">
         <v>58</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G4">
         <v>6</v>
@@ -614,13 +602,13 @@
         <v>3</v>
       </c>
       <c r="J4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="L4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M4">
         <v>1</v>
@@ -637,22 +625,22 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
         <v>58</v>
       </c>
       <c r="F5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G5">
         <v>7.5</v>
@@ -664,13 +652,13 @@
         <v>6</v>
       </c>
       <c r="J5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K5" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="L5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -687,22 +675,22 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E6" t="s">
         <v>58</v>
       </c>
       <c r="F6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G6">
         <v>10</v>
@@ -714,13 +702,13 @@
         <v>10</v>
       </c>
       <c r="J6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K6" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="L6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="M6">
         <v>2</v>
@@ -747,39 +735,39 @@
         <v>24</v>
       </c>
       <c r="B1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1" t="s">
         <v>82</v>
-      </c>
-      <c r="C1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F1" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" t="s">
         <v>87</v>
       </c>
-      <c r="B2" t="s">
+      <c r="F2" t="s">
         <v>88</v>
-      </c>
-      <c r="C2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F2" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="3">
@@ -787,10 +775,10 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D3">
         <v>0.82</v>
@@ -807,10 +795,10 @@
         <v>55</v>
       </c>
       <c r="B4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D4">
         <v>0.18</v>
@@ -827,10 +815,10 @@
         <v>55</v>
       </c>
       <c r="B5" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D5">
         <v>0.06</v>
@@ -844,13 +832,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D6">
         <v>0.65</v>
@@ -864,13 +852,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B7" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D7">
         <v>0.35</v>
@@ -884,13 +872,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B8" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D8">
         <v>0.14</v>
@@ -904,13 +892,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D9">
         <v>0.05</v>
@@ -924,13 +912,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B10" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D10">
         <v>0.55</v>
@@ -944,13 +932,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B11" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D11">
         <v>0.48</v>
@@ -964,13 +952,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B12" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D12">
         <v>0.22</v>
@@ -984,13 +972,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B13" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D13">
         <v>0.04</v>
@@ -1004,13 +992,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D14">
         <v>0.42</v>
@@ -1024,13 +1012,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B15" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D15">
         <v>0.38</v>
@@ -1044,13 +1032,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B16" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D16">
         <v>0.12</v>
@@ -1064,13 +1052,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B17" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C17" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D17">
         <v>0.03</v>

--- a/Assets/Excel/monster_explore.xlsx
+++ b/Assets/Excel/monster_explore.xlsx
@@ -6,6 +6,8 @@
     <sheet name="works" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="actions" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="loot" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="work_levels" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="action_levels" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -741,7 +743,6 @@
           <t>林缘哨道</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>林缘哨道 · 布陷</t>
@@ -761,7 +762,6 @@
           <t>村外林缘常有史莱姆出没。布下小陷阱，等魔物踩中后搜刮残骸。</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>small_trap</t>
@@ -801,7 +801,6 @@
           <t>溪谷岔路</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>溪谷岔路 · 布陷</t>
@@ -821,7 +820,6 @@
           <t>岔路口泥泞，魔物足迹杂乱。仍用小陷阱，但掉落种类更杂。</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>small_trap</t>
@@ -861,7 +859,6 @@
           <t>旧矿道口</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>旧矿道口 · 布陷</t>
@@ -881,7 +878,6 @@
           <t>废弃矿道口盘踞着更凶的魔物，需大陷阱才能稳妥收网。</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>large_trap</t>
@@ -921,7 +917,6 @@
           <t>坠星裂隙</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>坠星裂隙 · 布陷</t>
@@ -941,7 +936,6 @@
           <t>裂隙边缘魔力紊乱，魔物更强也更稀有。大陷阱每次要消耗两份才够稳。</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>large_trap</t>
@@ -1431,4 +1425,2640 @@
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B162"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>升到下级所需经验</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>xp</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>2091</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="n">
+        <v>2272</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="n">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="n">
+        <v>2460</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="n">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="n">
+        <v>2655</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="n">
+        <v>2755</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="n">
+        <v>2858</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="n">
+        <v>2961</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="n">
+        <v>3067</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="n">
+        <v>3175</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="n">
+        <v>3284</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="n">
+        <v>3395</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="n">
+        <v>3508</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="n">
+        <v>3623</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="n">
+        <v>3739</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="n">
+        <v>3857</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="n">
+        <v>3978</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="n">
+        <v>4099</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="n">
+        <v>4223</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="n">
+        <v>4349</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="n">
+        <v>4476</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="n">
+        <v>4605</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="n">
+        <v>4736</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="n">
+        <v>4869</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="n">
+        <v>5003</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="n">
+        <v>5139</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="n">
+        <v>5278</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="n">
+        <v>5417</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="n">
+        <v>5559</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="n">
+        <v>5703</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="n">
+        <v>5848</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="n">
+        <v>5995</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="n">
+        <v>6144</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="n">
+        <v>6295</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="n">
+        <v>6447</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="n">
+        <v>6601</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="n">
+        <v>6758</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="n">
+        <v>6915</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="n">
+        <v>7075</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="n">
+        <v>7237</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="n">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="n">
+        <v>7565</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" t="n">
+        <v>7732</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" t="n">
+        <v>7901</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" t="n">
+        <v>8071</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" t="n">
+        <v>8243</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" t="n">
+        <v>8418</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" t="n">
+        <v>8593</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" t="n">
+        <v>8771</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" t="n">
+        <v>8951</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" t="n">
+        <v>9132</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" t="n">
+        <v>9315</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" t="n">
+        <v>9500</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="n">
+        <v>9687</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" t="n">
+        <v>9875</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="n">
+        <v>10065</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="n">
+        <v>10258</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" t="n">
+        <v>10451</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" t="n">
+        <v>10647</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" t="n">
+        <v>10845</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" t="n">
+        <v>11044</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" t="n">
+        <v>11245</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" t="n">
+        <v>11448</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" t="n">
+        <v>11653</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" t="n">
+        <v>11859</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" t="n">
+        <v>12067</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" t="n">
+        <v>12278</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" t="n">
+        <v>12489</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" t="n">
+        <v>12703</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" t="n">
+        <v>12919</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" t="n">
+        <v>13136</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" t="n">
+        <v>13355</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" t="n">
+        <v>13576</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" t="n">
+        <v>13799</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" t="n">
+        <v>14023</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" t="n">
+        <v>14249</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" t="n">
+        <v>14478</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" t="n">
+        <v>14707</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" t="n">
+        <v>14939</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" t="n">
+        <v>15173</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" t="n">
+        <v>15408</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" t="n">
+        <v>15645</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" t="n">
+        <v>15884</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" t="n">
+        <v>16125</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" t="n">
+        <v>16367</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" t="n">
+        <v>16611</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" t="n">
+        <v>16858</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" t="n">
+        <v>17105</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" t="n">
+        <v>17355</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" t="n">
+        <v>17607</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" t="n">
+        <v>17860</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" t="n">
+        <v>18115</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" t="n">
+        <v>18372</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" t="n">
+        <v>18631</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" t="n">
+        <v>18891</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" t="n">
+        <v>19153</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" t="n">
+        <v>19418</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" t="n">
+        <v>19683</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" t="n">
+        <v>19951</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" t="n">
+        <v>20221</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" t="n">
+        <v>20492</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" t="n">
+        <v>20765</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" t="n">
+        <v>21040</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" t="n">
+        <v>21317</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" t="n">
+        <v>21595</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" t="n">
+        <v>21875</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" t="n">
+        <v>22158</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" t="n">
+        <v>22441</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" t="n">
+        <v>22727</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" t="n">
+        <v>23015</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" t="n">
+        <v>23304</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" t="n">
+        <v>23595</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" t="n">
+        <v>23888</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" t="n">
+        <v>24183</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" t="n">
+        <v>24479</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" t="n">
+        <v>24777</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" t="n">
+        <v>25078</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" t="n">
+        <v>25379</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" t="n">
+        <v>25683</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" t="n">
+        <v>25989</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>159</v>
+      </c>
+      <c r="B161" t="n">
+        <v>26296</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>160</v>
+      </c>
+      <c r="B162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B162"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>升到下级所需经验</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>xp</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>2091</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="n">
+        <v>2272</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="n">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="n">
+        <v>2460</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="n">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="n">
+        <v>2655</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="n">
+        <v>2755</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="n">
+        <v>2858</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="n">
+        <v>2961</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="n">
+        <v>3067</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="n">
+        <v>3175</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="n">
+        <v>3284</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="n">
+        <v>3395</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="n">
+        <v>3508</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="n">
+        <v>3623</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="n">
+        <v>3739</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="n">
+        <v>3857</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="n">
+        <v>3978</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="n">
+        <v>4099</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="n">
+        <v>4223</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="n">
+        <v>4349</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="n">
+        <v>4476</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="n">
+        <v>4605</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="n">
+        <v>4736</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="n">
+        <v>4869</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="n">
+        <v>5003</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="n">
+        <v>5139</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="n">
+        <v>5278</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="n">
+        <v>5417</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="n">
+        <v>5559</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="n">
+        <v>5703</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="n">
+        <v>5848</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="n">
+        <v>5995</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="n">
+        <v>6144</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="n">
+        <v>6295</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="n">
+        <v>6447</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="n">
+        <v>6601</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="n">
+        <v>6758</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="n">
+        <v>6915</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="n">
+        <v>7075</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="n">
+        <v>7237</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="n">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="n">
+        <v>7565</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" t="n">
+        <v>7732</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" t="n">
+        <v>7901</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" t="n">
+        <v>8071</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" t="n">
+        <v>8243</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" t="n">
+        <v>8418</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" t="n">
+        <v>8593</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" t="n">
+        <v>8771</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" t="n">
+        <v>8951</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" t="n">
+        <v>9132</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" t="n">
+        <v>9315</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" t="n">
+        <v>9500</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="n">
+        <v>9687</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" t="n">
+        <v>9875</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="n">
+        <v>10065</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="n">
+        <v>10258</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" t="n">
+        <v>10451</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" t="n">
+        <v>10647</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" t="n">
+        <v>10845</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" t="n">
+        <v>11044</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" t="n">
+        <v>11245</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" t="n">
+        <v>11448</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" t="n">
+        <v>11653</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" t="n">
+        <v>11859</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" t="n">
+        <v>12067</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" t="n">
+        <v>12278</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" t="n">
+        <v>12489</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" t="n">
+        <v>12703</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" t="n">
+        <v>12919</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" t="n">
+        <v>13136</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" t="n">
+        <v>13355</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" t="n">
+        <v>13576</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" t="n">
+        <v>13799</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" t="n">
+        <v>14023</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" t="n">
+        <v>14249</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" t="n">
+        <v>14478</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" t="n">
+        <v>14707</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" t="n">
+        <v>14939</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" t="n">
+        <v>15173</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" t="n">
+        <v>15408</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" t="n">
+        <v>15645</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" t="n">
+        <v>15884</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" t="n">
+        <v>16125</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" t="n">
+        <v>16367</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" t="n">
+        <v>16611</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" t="n">
+        <v>16858</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" t="n">
+        <v>17105</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" t="n">
+        <v>17355</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" t="n">
+        <v>17607</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" t="n">
+        <v>17860</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" t="n">
+        <v>18115</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" t="n">
+        <v>18372</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" t="n">
+        <v>18631</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" t="n">
+        <v>18891</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" t="n">
+        <v>19153</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" t="n">
+        <v>19418</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" t="n">
+        <v>19683</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" t="n">
+        <v>19951</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" t="n">
+        <v>20221</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" t="n">
+        <v>20492</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" t="n">
+        <v>20765</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" t="n">
+        <v>21040</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" t="n">
+        <v>21317</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" t="n">
+        <v>21595</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" t="n">
+        <v>21875</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" t="n">
+        <v>22158</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" t="n">
+        <v>22441</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" t="n">
+        <v>22727</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" t="n">
+        <v>23015</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" t="n">
+        <v>23304</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" t="n">
+        <v>23595</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" t="n">
+        <v>23888</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" t="n">
+        <v>24183</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" t="n">
+        <v>24479</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" t="n">
+        <v>24777</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" t="n">
+        <v>25078</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" t="n">
+        <v>25379</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" t="n">
+        <v>25683</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" t="n">
+        <v>25989</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>159</v>
+      </c>
+      <c r="B161" t="n">
+        <v>26296</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>160</v>
+      </c>
+      <c r="B162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+</worksheet>
 </file>
--- a/Assets/Excel/monster_explore.xlsx
+++ b/Assets/Excel/monster_explore.xlsx
@@ -443,22 +443,22 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>地区熟练度基数</t>
+          <t>动作熟练度基数</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>地区熟练度每级增量</t>
+          <t>动作熟练度每级增量</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否加工作XP(1/0)</t>
+          <t>是否加总等级XP(1/0)</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>是否加地区XP(1/0)</t>
+          <t>是否加动作熟练度XP(1/0)</t>
         </is>
       </c>
     </row>
@@ -490,12 +490,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>sceneXpBase</t>
+          <t>actionXpBase</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>sceneXpPerLevel</t>
+          <t>actionXpPerLevel</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -505,7 +505,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>grantSceneXp</t>
+          <t>grantActionXp</t>
         </is>
       </c>
     </row>
